--- a/素材對照清單.xlsx
+++ b/素材對照清單.xlsx
@@ -11,10 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材（曝品）清單" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用說明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LOGO清單'!$A$1:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'素材（曝品）清單'!$A$1:$I$17</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -31,43 +28,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="10"/>
+      <color rgb="000563C1"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <color rgb="000563C1"/>
-      <sz val="10"/>
-      <u val="single"/>
+      <b val="1"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00EE4D2D"/>
       <sz val="14"/>
     </font>
+    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -118,31 +100,31 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -230,264 +212,439 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1238250" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="371475"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="266700"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1238250" cy="219075"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>2</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="371475"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>3</row>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="161925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="161925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="409575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="304800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="533400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="228600"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="257175"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="152400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="161925"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>9</row>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1238250" cy="295275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1238250" cy="171450"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="409575"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="304800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="533400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -510,7 +667,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="600075"/>
+    <ext cx="1238250" cy="590550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -660,59 +817,59 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1066800" cy="723900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1066800" cy="723900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1076325" cy="723900"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1076325" cy="723900"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1076325" cy="723900"/>
-    <pic>
-      <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -785,7 +942,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1190625" cy="723900"/>
+    <ext cx="1181100" cy="723900"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -810,7 +967,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="704850"/>
+    <ext cx="1238250" cy="695325"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -885,7 +1042,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="809625" cy="723900"/>
+    <ext cx="800100" cy="723900"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -893,6 +1050,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1000125" cy="723900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1195,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1258,7 +1440,7 @@
           <t>造節</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>新品OOTD</t>
@@ -1271,7 +1453,7 @@
 OOTD_LOGO</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>new-arrival-ootd_logo.png</t>
         </is>
@@ -1286,7 +1468,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -1298,7 +1480,7 @@
           <t>造節</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>蝦皮婦幼展</t>
@@ -1310,7 +1492,7 @@
 婦幼展</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>shopee-mom-baby-expo_logo.png</t>
         </is>
@@ -1325,7 +1507,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -1337,7 +1519,7 @@
           <t>造節</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>甜蜜穿搭季</t>
@@ -1349,7 +1531,7 @@
 穿搭季</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>sweet-outfit-season_logo.png</t>
         </is>
@@ -1364,7 +1546,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -1373,28 +1555,28 @@
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>全站大促</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n"/>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4.4購物節</t>
+          <t>3C資訊展</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4.4購物節</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>44sale_logo.png</t>
+          <t>3C資訊展</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>3c-digital-expo_logo.png</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>system-elements\site-wide-sale\</t>
+          <t>system-elements\festival\</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1402,7 +1584,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -1411,36 +1593,37 @@
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>全站大促</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18號會員日</t>
+          <t>蝦皮內衣節</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18號會員日</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>memberday18_logo.png</t>
+          <t>內衣節
+蝦皮內衣節</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>underwear-festival_logo.png</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>system-elements\site-wide-sale\</t>
+          <t>system-elements\festival\</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>#ffa200／#ffff3c</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -1452,137 +1635,213 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
+      <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4.4購物節</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4.4購物節</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>44sale_logo.png</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\site-wide-sale\</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>全站大促</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>18號會員日</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18號會員日</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>memberday18_logo.png</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\site-wide-sale\</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>#ffa200／#ffff3c</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>全站大促</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>10.10品牌週年慶</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>10.10品牌週年慶
 10.10品牌週年慶\01_LOGO
 10.10品牌週年慶/01_LOGO</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>1010anniversary_logo.png</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>商城25節</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>商城25節
 01_LOGO\LOGO_白字_無USP
 01_LOGO/LOGO_白字_無USP</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>mall25festival_logo.png</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>#d0011d／#ffe600</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="62" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>（無圖）</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>99大促</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>99大促
 9.9品牌週年慶
 99品牌週年慶</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>99brandsale_logo.png</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>尚未放入圖檔</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>618大促</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>618大促
 618全民年中慶
@@ -1590,148 +1849,340 @@
 618大促/01_LOGO</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>618sale_logo.png</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>蝦皮直營</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>蝦皮直營
 Shopee直營</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>shopee-official-store_logo.png</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>蝦皮直營3C家電</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>蝦皮直營3C家電
+蝦皮直營 3C家電
+蝦皮直營+3C家電</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>shopee-official-store-3c_logo.png</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\common\</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="62" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>常用建檔</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>品牌會員</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>品牌會員</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>brand-member_logo.jpg</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\common\</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>#EE4D2D／#FFF600</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="62" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>常用建檔</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>限時特賣</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>限時特賣
 限時特賣_LOGO</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>limited-time-sale_logo.png</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>#fd5401／#f9ff39
 #084cb1／#fce700
 #d0011b／#fce700</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>屈臣氏</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>屈臣氏
 Watsons</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>watsons_logo.png</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>常用建檔</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>美妝保健館</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>美妝保健館</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>beauty-health-store_logo.png</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\common\</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>常用建檔</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>品牌旗艦</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>品牌旗艦</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>brand-flagship_logo.png</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\common\</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="62" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>常用建檔</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Apple授權經銷商</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Apple授權經銷商
+Apple 授權經銷商</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>apple-authorized-reseller_logo.png</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\common\</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -1740,13 +2191,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
 </worksheet>
 </file>
 
@@ -1756,7 +2214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1825,8 +2283,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>全站券*1</t>
         </is>
@@ -1836,7 +2294,7 @@
           <t>全站</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>sitewide_product-coupon-x1.png</t>
         </is>
@@ -1856,7 +2314,7 @@
           <t>#ee4d2d</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -1868,8 +2326,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>商城券*1</t>
         </is>
@@ -1879,7 +2337,7 @@
           <t>商城</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>mall_product-coupon-x1.png</t>
         </is>
@@ -1899,7 +2357,7 @@
           <t>#d0011b</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -1911,8 +2369,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>商城券*2</t>
         </is>
@@ -1922,7 +2380,7 @@
           <t>商城</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>mall_product-coupon-x2.png</t>
         </is>
@@ -1942,7 +2400,7 @@
           <t>#d0011b</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -1954,8 +2412,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>免運車</t>
         </is>
@@ -1965,7 +2423,7 @@
           <t>商城</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>mall_free-shipping-cart.png</t>
         </is>
@@ -1985,7 +2443,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -1997,8 +2455,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>蝦幣堆</t>
         </is>
@@ -2008,7 +2466,7 @@
           <t>全站</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>shopee-coins-pile.png</t>
         </is>
@@ -2028,7 +2486,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2040,8 +2498,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>全站券*2</t>
         </is>
@@ -2051,7 +2509,7 @@
           <t>全站</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>sitewide_product-coupon-x2.png</t>
         </is>
@@ -2071,7 +2529,7 @@
           <t>#ee4d2d</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2083,8 +2541,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>全站券*1+商城券*1</t>
         </is>
@@ -2094,7 +2552,7 @@
           <t>全站+商城</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>sitewide-mall_product-coupon-combo.png</t>
         </is>
@@ -2115,7 +2573,7 @@
 第2張 #ee4d2d</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2127,8 +2585,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>全站券*1+蝦幣堆</t>
         </is>
@@ -2138,7 +2596,7 @@
           <t>全站</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>sitewide-coupon_shrimp-coins-combo.png</t>
         </is>
@@ -2158,7 +2616,7 @@
           <t>#ee4d2d</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2170,8 +2628,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>商城券*1+蝦幣堆</t>
         </is>
@@ -2181,7 +2639,7 @@
           <t>商城</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>mall-coupon_shrimp-coins-combo.png</t>
         </is>
@@ -2201,7 +2659,7 @@
           <t>#d0011b</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2213,8 +2671,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>VIP券*1+蝦幣堆</t>
         </is>
@@ -2224,7 +2682,7 @@
           <t>VIP</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>vip-coupon_shrimp-coins-combo.png</t>
         </is>
@@ -2244,7 +2702,7 @@
           <t>#ff770f</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2256,8 +2714,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>直營券*1</t>
         </is>
@@ -2267,7 +2725,7 @@
           <t>直營</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>exclusive_product-coupon-x1.png</t>
         </is>
@@ -2287,7 +2745,7 @@
           <t>#d0011b</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2299,8 +2757,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>VIP券*1</t>
         </is>
@@ -2310,7 +2768,7 @@
           <t>VIP</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>vip_product-coupon-x1.png</t>
         </is>
@@ -2330,7 +2788,7 @@
           <t>#ff770f</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2342,8 +2800,8 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>免運車+免運券*1</t>
         </is>
@@ -2353,7 +2811,7 @@
           <t>免運</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>free-shipping-cart_coupon-combo.png</t>
         </is>
@@ -2373,7 +2831,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2385,10 +2843,10 @@
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>限時特賣-黃</t>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>CFS-娛樂</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2396,7 +2854,7 @@
           <t>限時特賣</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>限時特賣-黃.png</t>
         </is>
@@ -2416,7 +2874,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2428,10 +2886,10 @@
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>限時特賣-藍</t>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>CFS-3C</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2439,7 +2897,7 @@
           <t>限時特賣</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>限時特賣-藍.png</t>
         </is>
@@ -2459,7 +2917,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2471,10 +2929,10 @@
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>限時特賣-紅</t>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>CFS-生活用品</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2482,7 +2940,7 @@
           <t>限時特賣</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>限時特賣-紅.png</t>
         </is>
@@ -2502,14 +2960,56 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>常用建檔</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>品牌會員</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>vip-gift-box.png</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>artwork\common\</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I17"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -2527,9 +3027,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -2547,27 +3048,26 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Mall SKBN 素材對照清單</t>
         </is>
       </c>
-      <c r="B1" s="9" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>專案的 data/asset-library.json 與 configs/material-text-style.js。這份清單是 2026-09-20 當下的快照，之後新增或修改素材，這份不會自動更新。</t>
+          <t>專案的 data/asset-library.json 與 configs/material-text-style.js。這份清單是 2026-09-29 當下的快照，之後新增或修改素材，這份不會自動更新。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>圖示底色</t>
         </is>
@@ -2579,7 +3079,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>點檔名</t>
         </is>
@@ -2590,12 +3090,8 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr"/>
-      <c r="B5" s="9" t="n"/>
-    </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>LOGO 怎麼比對</t>
         </is>
@@ -2607,7 +3103,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr"/>
+      <c r="A7" s="10" t="n"/>
       <c r="B7" s="9" t="inlineStr">
         <is>
           <t>1. 工單的「品牌」欄或「LOGO」欄，跟資料庫「品牌名稱」有互相包含（例如寫「婦幼展」會比對到「蝦皮婦幼展」）。</t>
@@ -2615,7 +3111,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr"/>
+      <c r="A8" s="10" t="n"/>
       <c r="B8" s="9" t="inlineStr">
         <is>
           <t>2. 工單文字裡「包含」LOGO清單第 4 欄的任何一個關鍵字（例如寫 Watsons 會比對到屈臣氏）。</t>
@@ -2623,7 +3119,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="9" t="inlineStr">
         <is>
           <t>3. LOGO 欄寫成含有 \ 或 / 的內建代碼（例如 10.10品牌週年慶\01_LOGO），只會查關鍵字。</t>
@@ -2631,31 +3127,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr"/>
+      <c r="A10" s="10" t="n"/>
       <c r="B10" s="9" t="inlineStr">
         <is>
           <t>關鍵字不分大小寫、不分全形半形，比對時會忽略空白。</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr"/>
-      <c r="B11" s="9" t="n"/>
-    </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>素材怎麼比對</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>工單「曝品」類型是「素材」時，素材欄要寫「素材（曝品）清單」第 3 欄的名稱，要完全一樣（例如 商城券*2、限時特賣-黃）。</t>
+          <t>工單「曝品」類型是「素材」時，素材欄要寫「素材（曝品）清單」第 3 欄的名稱，要完全一樣（例如 商城券*2、CFS-娛樂）。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>商品怎麼比對</t>
         </is>
@@ -2666,12 +3158,8 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr"/>
-      <c r="B14" s="9" t="n"/>
-    </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>專屬色票</t>
         </is>
@@ -2683,7 +3171,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>檔案狀態</t>
         </is>
@@ -2695,7 +3183,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>未列入</t>
         </is>

--- a/素材對照清單.xlsx
+++ b/素材對照清單.xlsx
@@ -95,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -126,6 +126,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -208,11 +214,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>0</colOff>
+      <colOff>66675</colOff>
       <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="209550"/>
+      <rowOff>276225</rowOff>
+    </from>
+    <ext cx="1238250" cy="219075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -233,9 +239,9 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>0</colOff>
+      <colOff>66675</colOff>
       <row>2</row>
-      <rowOff>0</rowOff>
+      <rowOff>200025</rowOff>
     </from>
     <ext cx="1238250" cy="371475"/>
     <pic>
@@ -258,9 +264,9 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>0</colOff>
+      <colOff>66675</colOff>
       <row>3</row>
-      <rowOff>0</rowOff>
+      <rowOff>276225</rowOff>
     </from>
     <ext cx="1238250" cy="228600"/>
     <pic>
@@ -283,9 +289,9 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>0</colOff>
+      <colOff>66675</colOff>
       <row>4</row>
-      <rowOff>0</rowOff>
+      <rowOff>257175</rowOff>
     </from>
     <ext cx="1238250" cy="266700"/>
     <pic>
@@ -308,11 +314,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>0</colOff>
+      <colOff>66675</colOff>
       <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="219075"/>
+      <rowOff>276225</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -333,318 +339,568 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>0</colOff>
+      <colOff>66675</colOff>
       <row>6</row>
-      <rowOff>0</rowOff>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>7</row>
+      <rowOff>266700</rowOff>
     </from>
     <ext cx="1238250" cy="247650"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>8</row>
+      <rowOff>266700</rowOff>
     </from>
     <ext cx="1238250" cy="247650"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>9</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>10</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>11</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>12</row>
+      <rowOff>352425</rowOff>
+    </from>
+    <ext cx="1238250" cy="171450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>13</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>14</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>15</row>
+      <rowOff>504825</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>16</row>
+      <rowOff>361950</rowOff>
     </from>
     <ext cx="1238250" cy="152400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>17</row>
+      <rowOff>314325</rowOff>
+    </from>
+    <ext cx="1238250" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>18</row>
+      <rowOff>314325</rowOff>
+    </from>
+    <ext cx="1238250" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>19</row>
+      <rowOff>257175</rowOff>
+    </from>
+    <ext cx="1238250" cy="257175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>20</row>
+      <rowOff>457200</rowOff>
     </from>
     <ext cx="1238250" cy="161925"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="161925"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>21</row>
+      <rowOff>180975</rowOff>
     </from>
     <ext cx="1238250" cy="409575"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>123825</colOff>
+      <row>22</row>
+      <rowOff>104775</rowOff>
     </from>
     <ext cx="1123950" cy="571500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="381000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>23</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1238250" cy="390525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>24</row>
+      <rowOff>238125</rowOff>
     </from>
     <ext cx="1238250" cy="304800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>25</row>
+      <rowOff>123825</rowOff>
     </from>
     <ext cx="1238250" cy="533400"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="228600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>26</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>27</row>
+      <rowOff>238125</rowOff>
     </from>
     <ext cx="1238250" cy="295275"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1238250" cy="171450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>28</row>
+      <rowOff>352425</rowOff>
+    </from>
+    <ext cx="1238250" cy="180975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -681,6 +937,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -706,6 +965,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -731,6 +993,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -756,6 +1021,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -781,6 +1049,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -806,6 +1077,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -831,6 +1105,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -856,6 +1133,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -881,6 +1161,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -906,6 +1189,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -931,6 +1217,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -956,6 +1245,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -981,6 +1273,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1006,6 +1301,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1031,6 +1329,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1056,6 +1357,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1081,6 +1385,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1377,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1409,7 +1716,7 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>工單可以寫的關鍵字
-（品牌欄或LOGO欄，寫任一個都會比對到）</t>
+（先看LOGO欄，比對不到再看檔期欄）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1441,12 +1748,12 @@
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>新品OOTD</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>新品OOTD
 新品 OOTD_LOGO
@@ -1481,12 +1788,12 @@
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>蝦皮婦幼展</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>蝦皮婦幼展
 婦幼展</t>
@@ -1520,12 +1827,12 @@
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>甜蜜穿搭季</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>甜蜜穿搭季
 穿搭季</t>
@@ -1558,13 +1865,13 @@
           <t>造節</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>3C資訊展</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>3C資訊展</t>
         </is>
@@ -1597,12 +1904,12 @@
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>蝦皮內衣節</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>內衣節
 蝦皮內衣節</t>
@@ -1635,20 +1942,21 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4.4購物節</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4.4購物節</t>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>1.11購物節</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>1.11
+1.11購物節</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>44sale_logo.png</t>
+          <t>111sale_logo.png</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1673,20 +1981,21 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>18號會員日</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18號會員日</t>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>2.2購物節</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>2.2
+2.2購物節</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>memberday18_logo.png</t>
+          <t>22sale_logo.png</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1696,7 +2005,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>#ffa200／#ffff3c</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1711,22 +2020,21 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>10.10品牌週年慶</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>10.10品牌週年慶
-10.10品牌週年慶\01_LOGO
-10.10品牌週年慶/01_LOGO</t>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>3.3購物節</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>3.3
+3.3購物節</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>1010anniversary_logo.png</t>
+          <t>33sale_logo.png</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1736,7 +2044,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>#ee4e2e／#fffd3e</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1751,22 +2059,21 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>商城25節</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>商城25節
-01_LOGO\LOGO_白字_無USP
-01_LOGO/LOGO_白字_無USP</t>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>4.4購物節</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>4.4
+4.4購物節</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>mall25festival_logo.png</t>
+          <t>44sale_logo.png</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1776,7 +2083,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>#d0011d／#ffe600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1791,26 +2098,21 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>（無圖）</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>99大促</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>99大促
-9.9品牌週年慶
-99品牌週年慶</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>99brandsale_logo.png</t>
+      <c r="B11" s="12" t="n"/>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>5.5購物節</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>5.5
+5.5購物節</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>55sale_logo.png</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1820,12 +2122,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>#ee4e2e／#fffd3e</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>尚未放入圖檔</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
         </is>
       </c>
     </row>
@@ -1835,13 +2137,52 @@
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>6.6購物節</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>6.6
+6.6購物節</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>66sale_logo.png</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\site-wide-sale\</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>全站大促</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>618大促</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>618大促
 618全民年中慶
@@ -1849,334 +2190,657 @@
 618大促/01_LOGO</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>618sale_logo.png</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>全站大促</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>7.7購物節</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>7.7
+7.7購物節</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>77sale_logo.png</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\site-wide-sale\</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="62" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>全站大促</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>8.8購物節</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>8.8
+8.8購物節</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>88sale_logo.png</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\site-wide-sale\</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="100" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>全站大促</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>9.9購物節</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>9.9
+9.9購物節
+99購物節
+99大促
+9.9品牌週年慶
+99品牌週年慶</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>99brandsale_logo.png</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\site-wide-sale\</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>#ee4e2e／#fffd3e</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>全站大促</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>10.10品牌週年慶</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>10.10
+10.10品牌週年慶
+10.10品牌週年慶\01_LOGO
+10.10品牌週年慶/01_LOGO</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>1010anniversary_logo.png</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\site-wide-sale\</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>#ee4e2e／#fffd3e</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>全站大促</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>11.11最強購物節</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>11.11
+11.11最強購物節</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>1111sale_logo.png</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\site-wide-sale\</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>全站大促</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>12.12狂歡生日慶</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>12.12
+12.12狂歡生日慶</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>1212birthday_logo.png</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\site-wide-sale\</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="62" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>全站大促</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>18號會員日</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>18號會員日
+18會員日</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>memberday18_logo.png</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\site-wide-sale\</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>#ffa200／#ffff3c</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="85" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>全站大促</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>商城25節</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>商城25節
+25號商城狂購節
+商城狂購節
+01_LOGO\LOGO_白字_無USP
+01_LOGO/LOGO_白字_無USP</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>mall25festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\site-wide-sale\</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>#d0011d／#ffe600</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="62" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營
 Shopee直營</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>shopee-official-store_logo.png</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="62" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營3C家電</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營3C家電
 蝦皮直營 3C家電
 蝦皮直營+3C家電</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>shopee-official-store-3c_logo.png</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="62" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="62" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>品牌會員</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>品牌會員</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>brand-member_logo.jpg</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>#EE4D2D／#FFF600</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="62" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>限時特賣</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>限時特賣
 限時特賣_LOGO</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>limited-time-sale_logo.png</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>#fd5401／#f9ff39
 #084cb1／#fce700
 #d0011b／#fce700</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="62" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>屈臣氏</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>屈臣氏
 Watsons</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>watsons_logo.png</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="62" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>美妝保健館</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>美妝保健館</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>beauty-health-store_logo.png</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="62" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="62" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>品牌旗艦</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>品牌旗艦</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>brand-flagship_logo.png</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="62" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="70" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>Apple授權經銷商</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Apple授權經銷商
-Apple 授權經銷商</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
+Apple 授權經銷商
+Apple授權經銷
+Apple經銷</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>apple-authorized-reseller_logo.png</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2193,18 +2857,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29"/>
 </worksheet>
 </file>
 
@@ -3062,7 +3736,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>專案的 data/asset-library.json 與 configs/material-text-style.js。這份清單是 2026-09-29 當下的快照，之後新增或修改素材，這份不會自動更新。</t>
+          <t>專案的 data/asset-library.json 與 configs/material-text-style.js。這份清單是 2026-10-02 當下的快照，之後新增或修改素材，這份不會自動更新。</t>
         </is>
       </c>
     </row>
@@ -3074,7 +3748,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>圖示的灰色底是為了讓白字 LOGO（例如 618）也看得見，不是圖檔本身的底色。</t>
+          <t>白字 LOGO（例如 618、各檔購物節、Apple）的圖示格加了灰色底，是為了看得見，不是圖檔本身的底色。</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3772,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>匯入工單時，先找「這週上傳的素材資料夾」有沒有同名檔案；找不到再查資料庫：</t>
+          <t>匯入工單時，先找「這週上傳的素材資料夾」有沒有同名檔案；找不到再查資料庫（2026-10-02 更新比對規則）：</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3780,7 @@
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>1. 工單的「品牌」欄或「LOGO」欄，跟資料庫「品牌名稱」有互相包含（例如寫「婦幼展」會比對到「蝦皮婦幼展」）。</t>
+          <t>1. 先看工單「LOGO」欄寫的文字，比對不到才看「檔期」欄。例如檔期寫「蝦皮直營」、LOGO 寫「Apple授權經銷商」，會帶入 Apple，不會被檔期欄搶走。</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3788,7 @@
       <c r="A8" s="10" t="n"/>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2. 工單文字裡「包含」LOGO清單第 4 欄的任何一個關鍵字（例如寫 Watsons 會比對到屈臣氏）。</t>
+          <t>2. 文字跟「品牌名稱」或第 4 欄任何一個關鍵字相符就算比對到；同時符合好幾筆時，挑「符合的字最長」的那一筆（寫「蝦皮直營3C家電」不會被「蝦皮直營」搶走）。只寫品牌名稱的一部分也可以（寫「婦幼展」會比對到「蝦皮婦幼展」）。</t>
         </is>
       </c>
     </row>
@@ -3129,6 +3803,13 @@
     <row r="10">
       <c r="A10" s="10" t="n"/>
       <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>4. 大促可以只寫日期（2.2、11.11、12.12…）。日期前後不能再接數字，所以 11.11 不會誤中 1.11，12.2、2.25 也不會誤中 2.2。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>關鍵字不分大小寫、不分全形半形，比對時會忽略空白。</t>
         </is>

--- a/素材對照清單.xlsx
+++ b/素材對照清單.xlsx
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">

--- a/素材對照清單.xlsx
+++ b/素材對照清單.xlsx
@@ -241,9 +241,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>2</row>
-      <rowOff>200025</rowOff>
-    </from>
-    <ext cx="1238250" cy="371475"/>
+      <rowOff>333375</rowOff>
+    </from>
+    <ext cx="1238250" cy="219075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -343,7 +343,7 @@
       <row>6</row>
       <rowOff>266700</rowOff>
     </from>
-    <ext cx="1238250" cy="238125"/>
+    <ext cx="1238250" cy="247650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -366,9 +366,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>7</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
+      <rowOff>257175</rowOff>
+    </from>
+    <ext cx="1238250" cy="257175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -391,9 +391,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>8</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
+      <rowOff>238125</rowOff>
+    </from>
+    <ext cx="1238250" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -416,9 +416,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>9</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="238125"/>
+      <rowOff>276225</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -441,9 +441,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>10</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="238125"/>
+      <rowOff>276225</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -466,9 +466,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>11</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1238250" cy="400050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -491,9 +491,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>12</row>
-      <rowOff>352425</rowOff>
-    </from>
-    <ext cx="1238250" cy="171450"/>
+      <rowOff>285750</rowOff>
+    </from>
+    <ext cx="1238250" cy="200025"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -516,9 +516,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>13</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
+      <rowOff>295275</rowOff>
+    </from>
+    <ext cx="1238250" cy="190500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -541,9 +541,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>14</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
+      <rowOff>238125</rowOff>
+    </from>
+    <ext cx="1238250" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -566,9 +566,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>15</row>
-      <rowOff>504825</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
+      <rowOff>276225</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -591,9 +591,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>16</row>
-      <rowOff>361950</rowOff>
-    </from>
-    <ext cx="1238250" cy="152400"/>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -616,9 +616,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>17</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1238250" cy="152400"/>
+      <rowOff>323850</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -641,9 +641,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>18</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1238250" cy="152400"/>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="342900"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -666,9 +666,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>19</row>
-      <rowOff>257175</rowOff>
-    </from>
-    <ext cx="1238250" cy="257175"/>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1238250" cy="400050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
@@ -691,9 +691,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>20</row>
-      <rowOff>457200</rowOff>
-    </from>
-    <ext cx="1238250" cy="161925"/>
+      <rowOff>276225</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -716,9 +716,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>21</row>
-      <rowOff>180975</rowOff>
-    </from>
-    <ext cx="1238250" cy="409575"/>
+      <rowOff>247650</rowOff>
+    </from>
+    <ext cx="1238250" cy="276225"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -739,11 +739,11 @@
   <oneCellAnchor>
     <from>
       <col>1</col>
-      <colOff>123825</colOff>
+      <colOff>66675</colOff>
       <row>22</row>
-      <rowOff>104775</rowOff>
-    </from>
-    <ext cx="1123950" cy="571500"/>
+      <rowOff>257175</rowOff>
+    </from>
+    <ext cx="1238250" cy="266700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -766,9 +766,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>23</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1238250" cy="390525"/>
+      <rowOff>476250</rowOff>
+    </from>
+    <ext cx="1238250" cy="304800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -791,9 +791,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>24</row>
-      <rowOff>238125</rowOff>
-    </from>
-    <ext cx="1238250" cy="304800"/>
+      <rowOff>304800</rowOff>
+    </from>
+    <ext cx="1238250" cy="266700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -816,9 +816,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>25</row>
-      <rowOff>123825</rowOff>
-    </from>
-    <ext cx="1238250" cy="533400"/>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -843,7 +843,7 @@
       <row>26</row>
       <rowOff>266700</rowOff>
     </from>
-    <ext cx="1238250" cy="238125"/>
+    <ext cx="1238250" cy="247650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -866,9 +866,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>27</row>
-      <rowOff>238125</rowOff>
-    </from>
-    <ext cx="1238250" cy="295275"/>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
@@ -891,16 +891,491 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>28</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>29</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>30</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>31</row>
       <rowOff>352425</rowOff>
     </from>
+    <ext cx="1238250" cy="171450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>32</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>33</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>34</row>
+      <rowOff>504825</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>35</row>
+      <rowOff>361950</rowOff>
+    </from>
+    <ext cx="1238250" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>36</row>
+      <rowOff>314325</rowOff>
+    </from>
+    <ext cx="1238250" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>37</row>
+      <rowOff>314325</rowOff>
+    </from>
+    <ext cx="1238250" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>38</row>
+      <rowOff>257175</rowOff>
+    </from>
+    <ext cx="1238250" cy="257175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>39</row>
+      <rowOff>457200</rowOff>
+    </from>
+    <ext cx="1238250" cy="161925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>40</row>
+      <rowOff>180975</rowOff>
+    </from>
+    <ext cx="1238250" cy="409575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>123825</colOff>
+      <row>41</row>
+      <rowOff>104775</rowOff>
+    </from>
+    <ext cx="1123950" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>42</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1238250" cy="390525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>43</row>
+      <rowOff>238125</rowOff>
+    </from>
+    <ext cx="1238250" cy="304800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>44</row>
+      <rowOff>123825</rowOff>
+    </from>
+    <ext cx="1238250" cy="533400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>45</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>46</row>
+      <rowOff>238125</rowOff>
+    </from>
+    <ext cx="1238250" cy="295275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>47</row>
+      <rowOff>352425</rowOff>
+    </from>
     <ext cx="1238250" cy="180975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1684,7 +2159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1781,7 +2256,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="62" customHeight="1">
+    <row r="3" ht="70" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>造節</t>
@@ -1796,7 +2271,9 @@
       <c r="D3" s="11" t="inlineStr">
         <is>
           <t>蝦皮婦幼展
-婦幼展</t>
+婦幼展
+婦幼節
+婦幼</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1939,250 +2416,1007 @@
     <row r="7" ht="62" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>美食年貨節</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>美食年貨節
+美食年貨</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>food-new-year-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>居家年貨節</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>居家年貨節
+居家年貨</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>home-new-year-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>開春送禮</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>開春送禮
+開春</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>spring-gifting_logo.png</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>新春閱讀節</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>新春閱讀節
+新春閱讀
+閱讀節</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>new-year-reading-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="62" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>寵愛女王節</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>寵愛女王節
+寵愛女王
+女王節</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>queens-day-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>開鞋季</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>開鞋季
+開鞋</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>shoe-season_logo.png</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>涼夏家電祭</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>涼夏家電祭
+涼夏家電
+涼夏</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>summer-appliance-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>狂購家電祭</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>狂購家電祭
+狂購家電</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>mega-appliance-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="62" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>年終出清</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>年終出清</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>year-end-clearance_logo.png</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="62" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮保健節</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮保健節
+保健節</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>shopee-health-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮寵物展</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮寵物展
+寵物展
+寵物節</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>shopee-pet-expo_logo.png</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮曬車節</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮曬車節
+曬車節
+晒車節
+曬車</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>shopee-auto-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>蝦MI節</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>蝦MI節
+蝦米節
+蝦MI
+蝦米</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>shopee-mi-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="62" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>果粉節</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>果粉節
+果粉</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>apple-fans-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>手機配件節</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>手機配件節
+手機配件
+配件節</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>mobile-accessories-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="62" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>從齒玩美</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>從齒玩美
+從齒完美
+從齒</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>oral-care-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="62" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>全民瘋運動</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>全民瘋運動
+瘋運動
+全民運動</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>sports-fever_logo.png</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="100" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>美食好康週報</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>美食好康週報
+美食好康周報
+好康週報
+好康周報
+美食週報
+美食周報</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>food-deals-weekly_logo.png</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="70" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮時尚週</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮時尚週
+蝦皮時尚周
+時尚週
+時尚周</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>shopee-fashion-week_logo.png</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>1.11購物節</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>1.11
 1.11購物節</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>111sale_logo.png</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="62" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>2.2購物節</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>2.2
 2.2購物節</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>22sale_logo.png</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="62" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>3.3購物節</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>3.3
 3.3購物節</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>33sale_logo.png</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="62" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>4.4購物節</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>4.4
 4.4購物節</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>44sale_logo.png</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="62" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>5.5購物節</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>5.5
 5.5購物節</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>55sale_logo.png</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="62" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>6.6購物節</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>6.6
 6.6購物節</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>66sale_logo.png</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="70" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>618大促</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>618大促
 618全民年中慶
@@ -2190,118 +3424,118 @@
 618大促/01_LOGO</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>618sale_logo.png</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>#ee4e2e／#fffd3e</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="62" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>7.7購物節</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>7.7
 7.7購物節</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>77sale_logo.png</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="62" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="62" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>8.8購物節</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>8.8
 8.8購物節</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>88sale_logo.png</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="100" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="100" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>9.9購物節</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>9.9
 9.9購物節
@@ -2311,40 +3545,40 @@
 99品牌週年慶</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>99brandsale_logo.png</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="70" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>10.10品牌週年慶</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>10.10
 10.10品牌週年慶
@@ -2352,157 +3586,157 @@
 10.10品牌週年慶/01_LOGO</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>1010anniversary_logo.png</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="62" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>11.11最強購物節</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>11.11
 11.11最強購物節</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>1111sale_logo.png</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="62" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="62" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>12.12狂歡生日慶</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>12.12
 12.12狂歡生日慶</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>1212birthday_logo.png</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="62" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="62" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>18號會員日</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>18號會員日
 18會員日</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>memberday18_logo.png</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>#ffa200／#ffff3c</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="85" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="85" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>商城25節</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>商城25節
 25號商城狂購節
@@ -2511,313 +3745,313 @@
 01_LOGO/LOGO_白字_無USP</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>mall25festival_logo.png</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>#d0011d／#ffe600</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="62" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="62" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營
 Shopee直營</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>shopee-official-store_logo.png</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="62" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="62" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營3C家電</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營3C家電
 蝦皮直營 3C家電
 蝦皮直營+3C家電</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>shopee-official-store-3c_logo.png</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="62" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="62" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>品牌會員</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>品牌會員</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>brand-member_logo.jpg</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>#EE4D2D／#FFF600</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="62" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="62" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>限時特賣</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D44" s="11" t="inlineStr">
         <is>
           <t>限時特賣
 限時特賣_LOGO</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>limited-time-sale_logo.png</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>#fd5401／#f9ff39
 #084cb1／#fce700
 #d0011b／#fce700</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="62" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="62" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>屈臣氏</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>屈臣氏
 Watsons</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>watsons_logo.png</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="62" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="62" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>美妝保健館</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>美妝保健館</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>beauty-health-store_logo.png</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="62" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="62" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>品牌旗艦</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>品牌旗艦</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>brand-flagship_logo.png</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="70" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="70" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="B48" s="12" t="n"/>
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>Apple授權經銷商</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>Apple授權經銷商
 Apple 授權經銷商
@@ -2825,22 +4059,22 @@
 Apple經銷</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>apple-authorized-reseller_logo.png</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -2876,9 +4110,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId48"/>
 </worksheet>
 </file>
 
@@ -3811,7 +5064,7 @@
     <row r="11">
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>關鍵字不分大小寫、不分全形半形，比對時會忽略空白。</t>
+          <t>5. 打錯一兩個字也比對得到（名稱 4 個字以上容許差 1 個字，8 個字以上容許差 2 個字；只看 LOGO 欄，名稱裡有數字的不適用）。只寫一部分、卻有兩張以上都符合時（例如「年貨節」「家電祭」），會列為比對不到，請寫完整一點。關鍵字不分大小寫、不分全形半形，比對時會忽略空白。</t>
         </is>
       </c>
     </row>

--- a/素材對照清單.xlsx
+++ b/素材對照清單.xlsx
@@ -232,6 +232,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -257,6 +260,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -282,6 +288,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -307,6 +316,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -332,6 +344,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -357,6 +372,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -382,6 +400,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -407,6 +428,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -432,6 +456,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -457,6 +484,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -482,6 +512,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -507,6 +540,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -532,6 +568,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -557,6 +596,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -582,6 +624,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -607,6 +652,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -632,6 +680,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -657,6 +708,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -682,6 +736,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -707,6 +764,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -732,6 +792,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -757,6 +820,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -782,6 +848,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -807,6 +876,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -832,6 +904,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -857,6 +932,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -882,6 +960,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -907,6 +988,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -932,6 +1016,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -957,6 +1044,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -982,6 +1072,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1007,6 +1100,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1032,6 +1128,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1057,6 +1156,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1082,6 +1184,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1107,6 +1212,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1132,6 +1240,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1157,6 +1268,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1182,6 +1296,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1207,6 +1324,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1232,6 +1352,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1257,6 +1380,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1282,6 +1408,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1307,6 +1436,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1332,6 +1464,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1357,6 +1492,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1382,6 +1520,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3898,7 +4039,8 @@
       <c r="D44" s="11" t="inlineStr">
         <is>
           <t>限時特賣
-限時特賣_LOGO</t>
+限時特賣_LOGO
+CFS</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -4967,7 +5109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5025,7 +5167,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>匯入工單時，先找「這週上傳的素材資料夾」有沒有同名檔案；找不到再查資料庫（2026-10-02 更新比對規則）：</t>
+          <t>匯入工單時，LOGO 欄寫「無」或「-」代表這一格不放 LOGO，不會比對。其他情況先找「這週上傳的素材資料夾」有沒有同名檔案；找不到再查資料庫（2026-10-02 更新比對規則）：</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5218,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>工單「曝品」類型是「素材」時，素材欄要寫「素材（曝品）清單」第 3 欄的名稱，要完全一樣（例如 商城券*2、CFS-娛樂）。</t>
+          <t>工單「曝品」類型是「素材」時，素材欄要寫「素材（曝品）清單」第 3 欄的名稱，要完全一樣（例如 商城券*2、CFS-娛樂）。工單這一欄是下拉選單，照選即可。</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5230,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>曝品類型是「商品」時，不看這份清單：先找這週素材資料夾裡同名的商品圖，找不到才用品牌名稱查資料庫。</t>
+          <t>曝品類型是「商品」時，不看這份清單：先找這週素材資料夾裡同名的商品圖（副檔名、空白、底線、連字號、括號、「複製」「Copy of」不影響，其餘要一樣），找不到才用品牌名稱查資料庫。LOGO 也是先用同樣方式找這週資料夾。</t>
         </is>
       </c>
     </row>
@@ -5125,6 +5267,90 @@
       <c r="B17" s="9" t="inlineStr">
         <is>
           <t>資料庫裡的「示例」佔位項目（示例活動、示例品牌）沒有列進來。掛標與 CTA 是全站固定素材，也不在這份清單。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>不放 LOGO</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>工單 LOGO 欄寫「無」或「-」（全形、半形的橫線都算）＝這一格不放 LOGO：不會比對、不會出警示，也不會改用檔期欄去帶 LOGO。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>大促配色</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>全站大促的日期 LOGO（1.11～12.12、618）匯入時，工單沒指定背景色就自動帶入橘底 #ee4e2e／黃字 #fffd3e；18號會員日、25號商城狂購節是各自的配色（見 LOGO 清單「專屬色票」欄）。造節 LOGO 沒有專屬色票。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>日期寫法</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>第一檔的 LOGO 是「1.11購物節」，工單要寫 1.11；寫 1.1 不會比對到。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>限時特賣</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>LOGO 欄寫「限時特賣」或「CFS」都會帶入限時特賣 LOGO。曝品欄的 CFS-娛樂／CFS-3C／CFS-生活用品是素材，另外比對，不受影響。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>強制白色</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>全站大促的 LOGO 匯入時固定開「強制白色」；造節、常用建檔是背景偏深才開。要留意：11.11、12.12 的彩色立體邊會一起變白；蝦皮時尚週是實心的黑白圖，開了會變成一整塊白色。需要原色時，在放大編輯面板把強制白色關掉。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>模糊比對提醒</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>差一兩個字被帶入時，畫面上不會另外提示。匯入後請掃一眼 LOGO 對不對。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>警示何時消失</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>右側警示會自動消失：「LOGO 比對不到」→那一格有了 LOGO；「商品／素材比對不到」→那一格有了商品圖；「沒有圖可以抓色、背景色維持版型預設」→手動指定了底色，或補上了 LOGO／商品圖。</t>
         </is>
       </c>
     </row>

--- a/素材對照清單.xlsx
+++ b/素材對照清單.xlsx
@@ -5159,6 +5159,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
@@ -5230,10 +5231,11 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>曝品類型是「商品」時，不看這份清單：先找這週素材資料夾裡同名的商品圖（副檔名、空白、底線、連字號、括號、「複製」「Copy of」不影響，其餘要一樣），找不到才用品牌名稱查資料庫。LOGO 也是先用同樣方式找這週資料夾。</t>
-        </is>
-      </c>
-    </row>
+          <t>曝品類型是「商品」時，不看這份清單：先找這週素材資料夾裡同名的商品圖，找不到才用品牌名稱查資料庫。副檔名、空白、底線、連字號、括號、「複製」「Copy of」不影響，其餘要一樣；工單寫的副檔名跟實際檔案不同也對得到（工單寫 .tif、檔案是 .png 沒關係）。商品名稱裡的「/」（例如 10/24_…）不當成資料夾路徑，會對到存成「10 24_…」的檔案。LOGO 也是先用同樣方式找這週資料夾（LOGO 欄的「/」「\」維持是內建代碼）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
@@ -5270,6 +5272,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
@@ -5326,7 +5329,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>全站大促的 LOGO 匯入時固定開「強制白色」；造節、常用建檔是背景偏深才開。要留意：11.11、12.12 的彩色立體邊會一起變白；蝦皮時尚週是實心的黑白圖，開了會變成一整塊白色。需要原色時，在放大編輯面板把強制白色關掉。</t>
+          <t>全站大促的 LOGO 匯入時固定開「強制白色」；造節、常用建檔是背景偏深才開。例外：蝦皮時尚週固定用原本的樣子（白底黑字＋黑底白字），不管背景深淺都不會自動反白。要留意：11.11、12.12 的彩色立體邊會一起變白，需要原色時在放大編輯面板把強制白色關掉。</t>
         </is>
       </c>
     </row>

--- a/素材對照清單.xlsx
+++ b/素材對照清單.xlsx
@@ -232,9 +232,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -260,9 +257,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -288,9 +282,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -316,9 +307,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -344,9 +332,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -372,9 +357,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -400,9 +382,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -428,9 +407,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -456,9 +432,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -484,9 +457,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -512,9 +482,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -540,9 +507,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -568,9 +532,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -596,9 +557,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -624,9 +582,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -652,9 +607,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -680,9 +632,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -708,9 +657,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -736,9 +682,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -764,9 +707,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -792,9 +732,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -820,9 +757,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -848,9 +782,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -876,9 +807,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -888,347 +816,311 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>25</row>
+      <rowOff>276225</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>26</row>
+      <rowOff>257175</rowOff>
+    </from>
+    <ext cx="1238250" cy="257175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>27</row>
+      <rowOff>333375</rowOff>
+    </from>
+    <ext cx="1238250" cy="209550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>28</row>
+      <rowOff>323850</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>29</row>
+      <rowOff>504825</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>30</row>
+      <rowOff>533400</rowOff>
+    </from>
+    <ext cx="1238250" cy="190500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>31</row>
+      <rowOff>466725</rowOff>
+    </from>
+    <ext cx="1238250" cy="142875"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>32</row>
+      <rowOff>247650</rowOff>
+    </from>
+    <ext cx="1238250" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>33</row>
+      <rowOff>323850</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>34</row>
+      <rowOff>238125</rowOff>
+    </from>
+    <ext cx="1238250" cy="295275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>35</row>
+      <rowOff>323850</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>36</row>
+      <rowOff>247650</rowOff>
+    </from>
+    <ext cx="1238250" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>37</row>
       <rowOff>266700</rowOff>
     </from>
     <ext cx="1238250" cy="238125"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>26</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>27</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>28</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="238125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>29</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="238125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>30</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>31</row>
-      <rowOff>352425</rowOff>
-    </from>
-    <ext cx="1238250" cy="171450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>32</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>33</row>
-      <rowOff>266700</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>34</row>
-      <rowOff>504825</rowOff>
-    </from>
-    <ext cx="1238250" cy="247650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>35</row>
-      <rowOff>361950</rowOff>
-    </from>
-    <ext cx="1238250" cy="152400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>36</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1238250" cy="152400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>37</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1238250" cy="152400"/>
-    <pic>
-      <nvPicPr>
         <cNvPr id="37" name="Image 37" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -1240,9 +1132,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1254,7 +1143,7 @@
       <row>38</row>
       <rowOff>257175</rowOff>
     </from>
-    <ext cx="1238250" cy="257175"/>
+    <ext cx="1238250" cy="371475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="38" name="Image 38" descr="Picture"/>
@@ -1268,9 +1157,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1280,9 +1166,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>39</row>
-      <rowOff>457200</rowOff>
-    </from>
-    <ext cx="1238250" cy="161925"/>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="39" name="Image 39" descr="Picture"/>
@@ -1296,9 +1182,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1308,9 +1191,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>40</row>
-      <rowOff>180975</rowOff>
-    </from>
-    <ext cx="1238250" cy="409575"/>
+      <rowOff>247650</rowOff>
+    </from>
+    <ext cx="1238250" cy="285750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="40" name="Image 40" descr="Picture"/>
@@ -1324,21 +1207,18 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>123825</colOff>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
       <row>41</row>
-      <rowOff>104775</rowOff>
-    </from>
-    <ext cx="1123950" cy="571500"/>
+      <rowOff>247650</rowOff>
+    </from>
+    <ext cx="1238250" cy="285750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="41" name="Image 41" descr="Picture"/>
@@ -1352,9 +1232,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1364,9 +1241,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>42</row>
-      <rowOff>190500</rowOff>
-    </from>
-    <ext cx="1238250" cy="390525"/>
+      <rowOff>323850</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="42" name="Image 42" descr="Picture"/>
@@ -1380,9 +1257,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1392,9 +1266,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>43</row>
-      <rowOff>238125</rowOff>
-    </from>
-    <ext cx="1238250" cy="304800"/>
+      <rowOff>295275</rowOff>
+    </from>
+    <ext cx="1238250" cy="190500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="43" name="Image 43" descr="Picture"/>
@@ -1408,9 +1282,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1420,9 +1291,9 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>44</row>
-      <rowOff>123825</rowOff>
-    </from>
-    <ext cx="1238250" cy="533400"/>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="44" name="Image 44" descr="Picture"/>
@@ -1436,9 +1307,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1464,9 +1332,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1476,53 +1341,747 @@
       <col>1</col>
       <colOff>66675</colOff>
       <row>46</row>
+      <rowOff>276225</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>47</row>
+      <rowOff>438150</rowOff>
+    </from>
+    <ext cx="1238250" cy="200025"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>48</row>
+      <rowOff>276225</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>49</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>50</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>51</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>52</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>53</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>54</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>55</row>
+      <rowOff>352425</rowOff>
+    </from>
+    <ext cx="1238250" cy="171450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>56</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>57</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>58</row>
+      <rowOff>504825</rowOff>
+    </from>
+    <ext cx="1238250" cy="247650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>59</row>
+      <rowOff>361950</rowOff>
+    </from>
+    <ext cx="1238250" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>60</row>
+      <rowOff>314325</rowOff>
+    </from>
+    <ext cx="1238250" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>61</row>
+      <rowOff>314325</rowOff>
+    </from>
+    <ext cx="1238250" cy="152400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>62</row>
+      <rowOff>257175</rowOff>
+    </from>
+    <ext cx="1238250" cy="257175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>63</row>
+      <rowOff>457200</rowOff>
+    </from>
+    <ext cx="1238250" cy="161925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>64</row>
+      <rowOff>180975</rowOff>
+    </from>
+    <ext cx="1238250" cy="409575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>123825</colOff>
+      <row>65</row>
+      <rowOff>104775</rowOff>
+    </from>
+    <ext cx="1123950" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>400050</colOff>
+      <row>66</row>
+      <rowOff>342900</rowOff>
+    </from>
+    <ext cx="571500" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>67</row>
+      <rowOff>190500</rowOff>
+    </from>
+    <ext cx="1238250" cy="390525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>68</row>
       <rowOff>238125</rowOff>
     </from>
+    <ext cx="1238250" cy="304800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>69</row>
+      <rowOff>123825</rowOff>
+    </from>
+    <ext cx="1238250" cy="533400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>70</row>
+      <rowOff>266700</rowOff>
+    </from>
+    <ext cx="1238250" cy="238125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>71</row>
+      <rowOff>238125</rowOff>
+    </from>
     <ext cx="1238250" cy="295275"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>66675</colOff>
-      <row>47</row>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>72</row>
       <rowOff>352425</rowOff>
     </from>
     <ext cx="1238250" cy="180975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>73</row>
+      <rowOff>304800</rowOff>
+    </from>
+    <ext cx="1238250" cy="266700"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>74</row>
+      <rowOff>276225</rowOff>
+    </from>
+    <ext cx="1238250" cy="228600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>66675</colOff>
+      <row>75</row>
+      <rowOff>438150</rowOff>
+    </from>
+    <ext cx="1238250" cy="190500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2300,7 +2859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2483,7 +3042,7 @@
           <t>造節</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n"/>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="11" t="inlineStr">
         <is>
           <t>3C資訊展</t>
@@ -3314,250 +3873,1222 @@
     <row r="26" ht="62" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>生活風格節</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>生活風格節
+生活風格
+風格節</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>lifestyle-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="62" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>美好生活節</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>美好生活節
+美好生活</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>good-life-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="70" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>車用百貨夏殺</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>車用百貨夏殺
+車用百貨
+車用夏殺
+夏殺</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>auto-goods-summer-sale_logo.png</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="70" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>享樂好食光</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>享樂好食光
+享樂好時光
+好食光
+享樂好食</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>good-food-time_logo.png</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="100" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>517吃貨節</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>517吃貨節
+5.17吃貨節
+5.17
+517吃貨
+吃貨節
+517</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>517-foodie-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="100" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>玩家收藏秘境</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>玩家收藏秘境
+玩家收藏祕境
+玩家收藏
+收藏秘境
+收藏祕境
+玩家秘境</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>collectors-realm_logo.png</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="85" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>娛樂非你BOOK</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>娛樂非你BOOK
+娛樂非你不可
+娛樂非你
+非你BOOK
+娛樂BOOK</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>entertainment-book_logo.png</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="62" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>保暖大賞</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>保暖大賞
+保暖大賞節</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>winter-warm-awards_logo.png</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="70" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>洗沐嘉年華</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>洗沐嘉年華
+洗沐嘉年
+洗沐節
+洗沐</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>bath-care-carnival_logo.png</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="62" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>夏出清</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>夏出清
+夏季出清
+夏日出清</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>summer-clearance_logo.png</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="70" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>付清購物車</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>付清購物車
+清空購物車
+付清購物
+付清</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>checkout-cart_logo.png</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="62" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>清涼一夏</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>清涼一夏
+清涼一下</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>cool-summer_logo.png</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="62" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>盛夏美肌日</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>盛夏美肌日
+盛夏美肌
+美肌日</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>summer-skin-day_logo.png</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="70" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>超狂美妝節</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>超狂美妝節
+超狂美妝
+美妝節
+Beauty Holics</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>beauty-holics_logo.png</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="62" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>Golden Day</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Golden Day
+GoldenDay
+黃金雨</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>golden-day_logo.png</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="62" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>感恩出清</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>感恩出清
+感恩節出清</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>thanksgiving-clearance_logo.png</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="62" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>感鞋有你</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>感鞋有你
+感謝有你
+感鞋</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>thanks-shoes_logo.png</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="70" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>聖誕送禮季</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>聖誕送禮季
+聖誕送禮
+聖誕禮物季
+聖誕</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>christmas-gifting_logo.png</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="62" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>運動大牌出清</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>運動大牌出清
+運動大牌
+運動出清</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>sports-brand-clearance_logo.png</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="62" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮中元節</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮中元節
+中元節
+中元</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>shopee-ghost-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="62" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮中秋節</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮中秋節
+中秋節
+中秋</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>shopee-mid-autumn-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="62" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>蝦蝦運動會</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>蝦蝦運動會
+蝦蝦運動
+運動會</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>shopee-sports-day_logo.png</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="85" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>禮享母親派對</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>禮享母親派對
+禮享母親
+母親派對
+母親節派對
+母親節</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>mothers-day-party_logo.png</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="62" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>造節</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮醫美節</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮醫美節
+醫美節
+醫美</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>shopee-medical-beauty-festival_logo.png</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\festival\</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="62" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>1.11購物節</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>1.11
 1.11購物節</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>111sale_logo.png</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="62" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="62" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="B51" s="12" t="n"/>
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>2.2購物節</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>2.2
 2.2購物節</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>22sale_logo.png</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="62" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="62" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>3.3購物節</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>3.3
 3.3購物節</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>33sale_logo.png</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="62" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="62" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="B53" s="12" t="n"/>
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>4.4購物節</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D53" s="11" t="inlineStr">
         <is>
           <t>4.4
 4.4購物節</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>44sale_logo.png</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="62" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="62" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="B54" s="12" t="n"/>
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>5.5購物節</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>5.5
 5.5購物節</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>55sale_logo.png</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="62" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="62" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="B55" s="12" t="n"/>
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>6.6購物節</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D55" s="11" t="inlineStr">
         <is>
           <t>6.6
 6.6購物節</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>66sale_logo.png</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="70" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="70" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="B56" s="12" t="n"/>
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>618大促</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D56" s="11" t="inlineStr">
         <is>
           <t>618大促
 618全民年中慶
@@ -3565,118 +5096,118 @@
 618大促/01_LOGO</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>618sale_logo.png</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="62" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="62" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="B57" s="12" t="n"/>
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>7.7購物節</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D57" s="11" t="inlineStr">
         <is>
           <t>7.7
 7.7購物節</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>77sale_logo.png</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="62" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="62" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="11" t="inlineStr">
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="11" t="inlineStr">
         <is>
           <t>8.8購物節</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>8.8
 8.8購物節</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>88sale_logo.png</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="100" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="100" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="B59" s="12" t="n"/>
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>9.9購物節</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D59" s="11" t="inlineStr">
         <is>
           <t>9.9
 9.9購物節
@@ -3686,40 +5217,40 @@
 99品牌週年慶</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>99brandsale_logo.png</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="70" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="70" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>10.10品牌週年慶</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D60" s="11" t="inlineStr">
         <is>
           <t>10.10
 10.10品牌週年慶
@@ -3727,157 +5258,157 @@
 10.10品牌週年慶/01_LOGO</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>1010anniversary_logo.png</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="62" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="62" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>11.11最強購物節</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D61" s="11" t="inlineStr">
         <is>
           <t>11.11
 11.11最強購物節</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>1111sale_logo.png</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="62" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="62" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="B62" s="12" t="n"/>
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>12.12狂歡生日慶</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D62" s="11" t="inlineStr">
         <is>
           <t>12.12
 12.12狂歡生日慶</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>1212birthday_logo.png</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>#ee4e2e／#fffd3e</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="62" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="62" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="B63" s="12" t="n"/>
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>18號會員日</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>18號會員日
 18會員日</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>memberday18_logo.png</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>#ffa200／#ffff3c</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="85" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="85" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>全站大促</t>
         </is>
       </c>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>商城25節</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D64" s="11" t="inlineStr">
         <is>
           <t>商城25節
 25號商城狂購節
@@ -3886,314 +5417,357 @@
 01_LOGO/LOGO_白字_無USP</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>mall25festival_logo.png</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>system-elements\site-wide-sale\</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>#d0011d／#ffe600</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="62" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="62" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營
 Shopee直營</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>shopee-official-store_logo.png</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="62" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="62" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營3C家電</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D66" s="11" t="inlineStr">
         <is>
           <t>蝦皮直營3C家電
 蝦皮直營 3C家電
 蝦皮直營+3C家電</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>shopee-official-store-3c_logo.png</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="62" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="100" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮直營生活超市</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮直營生活超市
+蝦皮直營 生活超市
+蝦皮直營+生活超市
+蝦皮直營_生活超市
+蝦皮直營-生活超市
+生活超市</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>shopee-official-store-supermarket_logo.jpg</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\common\</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="62" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>常用建檔</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>品牌會員</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D68" s="11" t="inlineStr">
         <is>
           <t>品牌會員</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>brand-member_logo.jpg</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>#EE4D2D／#FFF600</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="62" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="62" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>限時特賣</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D69" s="11" t="inlineStr">
         <is>
           <t>限時特賣
 限時特賣_LOGO
 CFS</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>limited-time-sale_logo.png</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>#fd5401／#f9ff39
 #084cb1／#fce700
 #d0011b／#fce700</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="62" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="62" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>屈臣氏</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D70" s="11" t="inlineStr">
         <is>
           <t>屈臣氏
 Watsons</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>watsons_logo.png</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="62" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="62" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>美妝保健館</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D71" s="11" t="inlineStr">
         <is>
           <t>美妝保健館</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>beauty-health-store_logo.png</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="62" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="62" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="11" t="inlineStr">
         <is>
           <t>品牌旗艦</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D72" s="11" t="inlineStr">
         <is>
           <t>品牌旗艦</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>brand-flagship_logo.png</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>已放入</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="70" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="70" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>常用建檔</t>
         </is>
       </c>
-      <c r="B48" s="12" t="n"/>
-      <c r="C48" s="11" t="inlineStr">
+      <c r="B73" s="12" t="n"/>
+      <c r="C73" s="11" t="inlineStr">
         <is>
           <t>Apple授權經銷商</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D73" s="11" t="inlineStr">
         <is>
           <t>Apple授權經銷商
 Apple 授權經銷商
@@ -4201,22 +5775,144 @@
 Apple經銷</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>apple-authorized-reseller_logo.png</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>system-elements\common\</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="70" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>常用建檔</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>Lux輕奢時尚</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>Lux輕奢時尚
+Lux 輕奢時尚
+輕奢時尚
+輕奢</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>lux-fashion_logo.png</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\common\</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="62" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>常用建檔</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮書城</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>蝦皮書城
+書城</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>shopee-bookstore_logo.png</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\common\</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>已放入</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="85" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>常用建檔</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>5號發薪補貨日</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>5號發薪補貨日
+發薪補貨日
+發薪補貨
+5號發薪
+發薪日</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>payday5-restock_logo.png</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>system-elements\common\</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>已放入</t>
         </is>
@@ -4271,9 +5967,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId48"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId76"/>
 </worksheet>
 </file>
 
@@ -5131,7 +6855,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>專案的 data/asset-library.json 與 configs/material-text-style.js。這份清單是 2026-10-02 當下的快照，之後新增或修改素材，這份不會自動更新。</t>
+          <t>專案的 data/asset-library.json 與 configs/material-text-style.js。這份清單是 2026-10-05 當下的快照，之後新增或修改素材，這份不會自動更新。</t>
         </is>
       </c>
     </row>
@@ -5159,7 +6883,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
@@ -5184,7 +6907,7 @@
       <c r="A8" s="10" t="n"/>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>2. 文字跟「品牌名稱」或第 4 欄任何一個關鍵字相符就算比對到；同時符合好幾筆時，挑「符合的字最長」的那一筆（寫「蝦皮直營3C家電」不會被「蝦皮直營」搶走）。只寫品牌名稱的一部分也可以（寫「婦幼展」會比對到「蝦皮婦幼展」）。</t>
+          <t>2. 文字跟「品牌名稱」或第 4 欄任何一個關鍵字相符就算比對到；同時符合好幾筆時，挑「符合的字最長」的那一筆（寫「蝦皮直營3C家電」「蝦皮直營生活超市」不會被「蝦皮直營」搶走）。只寫品牌名稱的一部分也可以（寫「婦幼展」會比對到「蝦皮婦幼展」）。</t>
         </is>
       </c>
     </row>
@@ -5235,7 +6958,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
@@ -5272,7 +6994,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
@@ -5329,7 +7050,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>全站大促的 LOGO 匯入時固定開「強制白色」；造節、常用建檔是背景偏深才開。例外：蝦皮時尚週固定用原本的樣子（白底黑字＋黑底白字），不管背景深淺都不會自動反白。要留意：11.11、12.12 的彩色立體邊會一起變白，需要原色時在放大編輯面板把強制白色關掉。</t>
+          <t>全站大促的 LOGO 匯入時固定開「強制白色」；造節、常用建檔是背景偏深才開。例外：蝦皮時尚週（白底黑字＋黑底白字）、蝦皮直營生活超市（目前是紅底方塊圖，沒有去背）固定用原本的樣子，不管背景深淺都不會自動反白。要留意：11.11、12.12 的彩色立體邊會一起變白，需要原色時在放大編輯面板把強制白色關掉。</t>
         </is>
       </c>
     </row>
